--- a/relatorios/contabilidade/ANA_CELIA_DIAS_TRABALHADOS_AGOSTO_2026.xlsx
+++ b/relatorios/contabilidade/ANA_CELIA_DIAS_TRABALHADOS_AGOSTO_2026.xlsx
@@ -1275,7 +1275,7 @@
     <row r="29">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t>Ela trabalhou sempre nas quartas, sextas e domingos — cobrindo as folgas da equipe. A única sexta sem venda no mês foi 21/08.</t>
+          <t>Dias da semana em que houve venda: domingo (5x), quarta (4x), sexta (3x).</t>
         </is>
       </c>
     </row>
